--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -924,7 +924,7 @@
     <t>Interprétation</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAObservationInterpretation|2.0.3-sd</t>
   </si>
   <si>
     <t>Observation.methodCode</t>
@@ -1593,7 +1593,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.01171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.4375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
